--- a/Paket_5_Bahasa_Indonesia_TKA_SD.xlsx
+++ b/Paket_5_Bahasa_Indonesia_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 5 Bahasa" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 1: contoh soal pemahaman teks.</t>
+          <t>Berdasarkan teks bacaan, di manakah letak geografis Taman Nasional Bunaken?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Di Teluk Tomini, Gorontalo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Di Teluk Manado, Sulawesi Utara</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Di Kepulauan Derawan, Kalimantan Timur</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Di Teluk Cenderawasih, Papua Barat</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 2: contoh soal pemahaman teks.</t>
+          <t>Apa penyebab terjadinya fenomena pemutihan karang (*coral bleaching*) di perairan laut Bunaken?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Terumbu karang dimangsa oleh kawanan lumba-lumba</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Suhu air laut yang terlalu hangat akibat pemanasan global</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Kurangnya kadar garam di perairan Teluk Manado</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Banyaknya dinding karang vertikal yang runtuh ke dasar laut</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 3: contoh soal pemahaman teks.</t>
+          <t>Makna istilah 'rehabilitasi' pada paragraf kedua teks informasi di atas adalah....</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Upaya penutupan total kawasan laut dari kunjungan wisatawan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Proses pemulihan dan perbaikan kembali ekosistem yang telah rusak ke kondisi semula</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Penjualan terumbu karang hias ke luar negeri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Penangkapan ikan karang menggunakan jaring modern</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,37 +592,41 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 4: contoh soal pemahaman teks.</t>
+          <t>Langkah nyata apa saja yang dilakukan pemerintah bersama komunitas penyelam lokal untuk menyelamatkan terumbu karang Bunaken?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Menerapkan teknik rehabilitasi karang buatan.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Melakukan aksi pembersihan sampah plastik secara berkala.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Menetapkan zona larangan tangkap bagi kapal penangkap ikan komersial.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Mengalirkan air tawar dalam jumlah besar ke dasar laut.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,7 +637,11 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,27 +651,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 5: contoh soal pemahaman teks.</t>
+          <t>Ide pokok yang terdapat pada paragraf pertama teks informasi di atas adalah....</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Kekayaan dan keanekaragaman hayati bawah laut Taman Nasional Bunaken</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Pencemaran limbah plastik di sungai Kota Manado</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Jadwal pelayaran kapal pesiar di perairan Sulawesi Utara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Bahaya menyelam di dinding karang curam vertikal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,17 +682,21 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 6: contoh soal pemahaman teks.</t>
+          <t>Tentukan kebenaran dari setiap pernyataan berikut berdasarkan teks informasi Bunaken!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -707,7 +727,11 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,27 +741,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 7: contoh soal pemahaman teks.</t>
+          <t>Simpulan yang paling tepat dari teks bacaan Taman Nasional Bunaken adalah.... Bacalah cerita fiksi berikut dengan cermat untuk menjawab soal nomor 8 sampai 14!
+Cahaya Lilin Kecil
+Malam itu, hujan lebat disertai petir melanda Desa Sukatani. Tiba-tiba, aliran listrik padam total dan suasana seketika menjadi gelap gulita. Di atas meja belajar kayu di kamar Rian, terdapat sebatang lilin kecil berwarna putih yang selama ini tersimpan di dalam laci berdebu. Lilin kecil itu merasa minder jika dibandingkan dengan lampu belajar listrik modern yang terang benderang.
+Ibu Rian masuk ke kamar sambil menyalakan pemantik api. Seketika itu juga, sumbu lilin menyala mengeluarkan api keemasan yang hangat. Kamar yang semula gulita pun menjadi terang temaram. Rian yang awalnya cemas karena belum menyelesaikan tugas sekolahnya langsung tersenyum gembira. "Alhamdulillah, sekarang aku bisa melanjutkan belajar matematika," seru Rian penuh semangat.
+Melihat Rian tekun belajar berkat pancaran cahayanya, lilin kecil merasa sangat bahagia. Meskipun tubuh lilinnya perlahan-lahan meleleh dan memendek seiring berjalannya waktu, ia tidak merasa kecewa atau menyesal sedikit pun. Lilin kecil itu bangga karena di akhir usianya, ia mampu memberikan manfaat nyata dan menerangi seseorang yang sedang berusaha meraih cita-citanya.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Bunaken merupakan surga bawah laut dunia yang sangat indah namun menghadapi ancaman lingkungan sehingga perlu upaya konservasi berkelanjutan.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Seluruh terumbu karang di Bunaken telah mati dan tidak dapat diperbaiki lagi.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Kapal nelayan dilarang berlayar di seluruh perairan laut Indonesia.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Pemanasan global hanya terjadi di kawasan Teluk Manado saja.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -748,7 +776,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +790,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 8: contoh soal pemahaman teks.</t>
+          <t>Bagaimana perasaan lilin kecil pada awal cerita sebelum sumbunya dinyalakan?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Sombong karena merasa dirinya paling berjasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Minder dan rendah diri jika dibandingkan dengan lampu belajar listrik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Gembira karena ditaruh di dalam laci meja yang gelap</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Marah karena tidak diperhatikan oleh Rian</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +821,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +835,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 9: contoh soal pemahaman teks.</t>
+          <t>Latar suasana yang tergambar pada awal cerita saat listrik padam adalah....</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Meriah dan penuh sorak sorai</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Gelap gulita, sunyi, dan mencekam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Tenang dan bersahaja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kacau balau karena ada banjir</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +866,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +880,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 10: contoh soal pemahaman teks.</t>
+          <t>Mengapa lilin kecil merasa bahagia meskipun tubuhnya harus meleleh dan memendek?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Karena api di sumbunya mengeluarkan panas yang membakar laci meja</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Karena ia bangga pancaran cahayanya dapat menerangi Rian yang sedang belajar menggapai cita-cita</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Karena ia tidak perlu disimpan lagi di dalam laci kamar yang berdebu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Karena ia berhasil mengalahkan terang lampu listrik modern</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,37 +911,41 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 11: contoh soal pemahaman teks.</t>
+          <t>Sifat dan keteladanan apa saja yang tercermin dari tokoh lilin kecil dalam cerita?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Rela berkorban demi memberikan manfaat bagi orang lain.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Ikhlas dan tidak menyesali pengorbanan dirinya.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Menuntut imbalan mahal atas cahaya yang ia berikan.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Menolak dinyalakan karena takut tubuhnya habis meleleh.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,7 +956,11 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -922,27 +970,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 12: contoh soal pemahaman teks.</t>
+          <t>Amanat moral yang dapat dipetik dari kisah lilin kecil adalah....</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Jangan pernah belajar saat listrik sedang padam di rumah.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Sebaik-baiknya hidup adalah yang mampu memberikan manfaat dan cahaya kebaikan bagi sesama walau dalam kesederhanaan.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Lampu listrik modern jauh lebih baik daripada lilin sederhana.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Gunakan pemantik api secara hati-hati agar tidak terluka.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -953,17 +1001,21 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 13: contoh soal pemahaman teks.</t>
+          <t>Tentukan kesesuaian dari pernyataan berikut terkait pesan keteladanan cerita lilin kecil!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -994,7 +1046,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1060,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 14: contoh soal pemahaman teks.</t>
+          <t>Ungkapan 'rendah diri' yang sempat dirasakan oleh lilin kecil memiliki makna yang sama dengan....</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Minder</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Rendah hati</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Besar kepala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Tinggi hati</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,7 +1091,11 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1045,27 +1105,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 15: contoh soal pemahaman teks.</t>
+          <t>Kalimat ajakan (persuasif) yang paling tepat untuk mengampanyekan gerakan hemat listrik adalah....</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Listrik padam menyebabkan kamar menjadi gelap gulita.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Matikan lampu dan peralatan elektronik jika tidak digunakan untuk masa depan bumi kita!</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Mengapa tagihan listrik bulan ini meningkat drastis?</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Pembangkit listrik tenaga surya dibangun di atap rumah warga.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1076,7 +1136,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1150,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 16: contoh soal pemahaman teks.</t>
+          <t>Penggunaan kata berimbuhan yang tepat terdapat pada kalimat....</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Kakak sedang menugaskan tugas matematika di meja belajar.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Kakak sedang mengerjakan tugas matematika di meja belajar.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Kakak sedang kerjakan tugas matematika di meja belajar.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kakak sedang diterjakan tugas matematika di meja belajar.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1181,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1195,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 17: contoh soal pemahaman teks.</t>
+          <t>Penulisan kata baku yang tepat terdapat pada kalimat....</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Para atlit nasional sedang berlatih keras demi menjaga stamina tubuh.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Para atlet nasional sedang berlatih keras demi menjaga stamina tubuh.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Para atlit nasional sedang berlatih keras demi menjaga setamina tubuh.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Para atlet nasional sedang berlatih keras demi menjaga setamina tubuh.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,37 +1226,43 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 18: contoh soal pemahaman teks.</t>
+          <t>Perhatikan kalimat berikut:
+"Buku itu saya sudah membacanya sampai selesai kemarin sore."
+Manakah perbaikan kalimat di atas yang TEPAT dan EFEKTIF?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Buku itu sudah saya baca sampai selesai kemarin sore.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Saya sudah membaca buku itu sampai selesai kemarin sore.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Buku itu dibaca oleh saya sudah selesai kemarin sore.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kemarin sore buku itu saya sudah membacanya tuntas.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,7 +1273,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1287,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 19: contoh soal pemahaman teks.</t>
+          <t>Perhatikan petunjuk acak penghematan energi listrik di rumah berikut:
+(1) Matikan kran air saat menyabuni piring cucian.
+(2) Buka jendela kamar pada pagi hari agar sirkulasi udara dan cahaya alami masuk.
+(3) Matikan pendingin ruangan (AC) dan gunakan kipas angin seperlunya.
+(4) Cabut steker kabel pengisi daya ponsel dari stopkontak setelah baterai penuh.
+Langkah-langkah di atas merupakan panduan praktis untuk....</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Mencegah korsleting listrik saat banjir</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Membiasakan perilaku hemat energi di lingkungan rumah tangga</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Memperbaiki jaringan kabel instalasi listrik rumah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Memasang pembangkit listrik tenaga surya mandiri</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1323,21 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Bahasa 20: contoh soal pemahaman teks.</t>
+          <t>Tentukan kebenaran penggunaan tanda koma (,) pada kalimat majemuk berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1368,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
